--- a/协作/28-决策记录.xlsx
+++ b/协作/28-决策记录.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -829,13 +829,137 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>决策-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>流程</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>是否保留「档位 / 门禁开关 / 可选交付物 / 分阶段路线」这些配置面</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>① 保留，由项目自选 ② 全角色全开、零配置（本版采用） ③ 分阶段启用（P0–P4）</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>选 ②：协议默认全开，删除全部人工配置面</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>用户明确要求「直接全角色全开，没有人工再去手动配置」；任何配置面都是可被跳过的入口。删除后偏离只能走账本例外，且 G8 前必须关闭</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>§1 §2.1 §2.3 §3 §5 §6 §14；40 份模板一次性铺满</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>用户+负责人</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TEAMODEL.md</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>已生效</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>决策-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>技术</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>模板 18 专项审查的「类别」枚举只有三项，但附件B 有兼容性/可运维性检查项</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>① 改附件B 删两个检查项 ② 扩枚举为五类（本版采用）</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>选 ②：扩为 安全/性能/供应链/兼容性/可运维性</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>附件B 是冻结文档（v1），且检查项本身有意义；只扩枚举即可让 B-06/B-07/B-08 合法落表，否则 G0 枚举校验必然失败</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>§5.18；模板/18-专项审查报告.xlsx；18 的记录</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>架构契约</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>模板-18</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>已生效</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"技术,产品,流程,资源"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
-      <formula1>"生效,已撤销"</formula1>
+    <dataValidation sqref="K2:K121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"生效,已生效,已撤销"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/协作/28-决策记录.xlsx
+++ b/协作/28-决策记录.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -950,6 +950,68 @@
       <c r="L8" t="inlineStr">
         <is>
           <t>证据-0008</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>决策-0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>流程</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>协议与模板放在使用方仓库还是独立仓库维护</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>① 继续放在 DCG 里随 DCG 提交 ② 独立成仓 TEAMODEL，DCG 按标签引用（本版采用）</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>选 ②：协议独立成仓，DCG 只保留自己写的交付物与记录</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>协议要跨项目复用；混在 DCG 提交历史里会把「协议演进」与「项目变更」耦合，且每个使用方各留一份模板必然漂移</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TEAMODEL.md、协作/模板/**、01 项目画像、13 文件所有权</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:30:00 +08:00</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>TEAMODEL 仓库</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>已生效</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>证据-0012</t>
         </is>
       </c>
     </row>
